--- a/dc5_milk_run_routes.xlsx
+++ b/dc5_milk_run_routes.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,366 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>route_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>dc</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>stores_served</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>number_of_stores</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>total_demand_cft</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>truck_selected</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>truck_capacity_cft</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>truck_utilization_percent</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>route_distance_km</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>monthly_cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>DPI64758 -&gt; DPI64692 -&gt; DPI63920 -&gt; DPI70100 -&gt; DPI66659 -&gt; DPI64476 -&gt; DPI66175 -&gt; DPI66646</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2" t="n">
+        <v>974</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1613</v>
+      </c>
+      <c r="G2" t="n">
+        <v>980</v>
+      </c>
+      <c r="H2" t="n">
+        <v>99.39</v>
+      </c>
+      <c r="I2" t="n">
+        <v>671.35</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1209191.12</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>DPI64647 -&gt; DPI66421 -&gt; DPI64378 -&gt; DPI67128 -&gt; DPI64303 -&gt; DPI64255 -&gt; DPI63822</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3" t="n">
+        <v>976</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1613</v>
+      </c>
+      <c r="G3" t="n">
+        <v>980</v>
+      </c>
+      <c r="H3" t="n">
+        <v>99.59</v>
+      </c>
+      <c r="I3" t="n">
+        <v>484.97</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1148037.43</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>DPI70179 -&gt; DPI70273 -&gt; DPI64651 -&gt; DPI66144 -&gt; DPI64746 -&gt; DPI64323 -&gt; DPI66692 -&gt; DPI64696 -&gt; DPI64104</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E4" t="n">
+        <v>970</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1613</v>
+      </c>
+      <c r="G4" t="n">
+        <v>980</v>
+      </c>
+      <c r="H4" t="n">
+        <v>98.98</v>
+      </c>
+      <c r="I4" t="n">
+        <v>952.55</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1301452.02</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>DPI64639 -&gt; DPI64044 -&gt; DPI63993 -&gt; DPI66460 -&gt; DPI64176 -&gt; DPI64234 -&gt; DPI66572 -&gt; DPI64149 -&gt; DPI70038 -&gt; DPI70073 -&gt; DPI64288 -&gt; DPI67024 -&gt; DPI70041</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>13</v>
+      </c>
+      <c r="E5" t="n">
+        <v>957</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1613</v>
+      </c>
+      <c r="G5" t="n">
+        <v>980</v>
+      </c>
+      <c r="H5" t="n">
+        <v>97.65000000000001</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1360.27</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1435224.38</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DFT80081 -&gt; DFT80066 -&gt; DFT80034 -&gt; DPI66508 -&gt; DPI64511 -&gt; DPI70002 -&gt; DPI70106 -&gt; DPI64236 -&gt; DPI66734 -&gt; DPI64352 -&gt; DPI67031 -&gt; DPI66684</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>12</v>
+      </c>
+      <c r="E6" t="n">
+        <v>936</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1613</v>
+      </c>
+      <c r="G6" t="n">
+        <v>980</v>
+      </c>
+      <c r="H6" t="n">
+        <v>95.51000000000001</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1133.02</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1360662.66</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DPI66092 -&gt; DPI64484 -&gt; DPI66327 -&gt; DPI63895 -&gt; DPI66335 -&gt; DPI63817 -&gt; DPI66229 -&gt; DPI64559 -&gt; DFT80087 -&gt; DPI70302</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="n">
+        <v>966</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1613</v>
+      </c>
+      <c r="G7" t="n">
+        <v>980</v>
+      </c>
+      <c r="H7" t="n">
+        <v>98.56999999999999</v>
+      </c>
+      <c r="I7" t="n">
+        <v>530.62</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1163017.46</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>DPI66263 -&gt; DPI64665 -&gt; DPI64502 -&gt; DPI70120 -&gt; DPI66402 -&gt; DPI64032 -&gt; DPI64409 -&gt; DPI66528 -&gt; DPI67198 -&gt; DPI70317</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="n">
+        <v>979</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1613</v>
+      </c>
+      <c r="G8" t="n">
+        <v>980</v>
+      </c>
+      <c r="H8" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="I8" t="n">
+        <v>632.4400000000001</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1196423.54</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DC_5</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DPI66264 -&gt; DPI64273 -&gt; DPI64179 -&gt; DPI63847 -&gt; DPI66262 -&gt; DPI70197 -&gt; DPI66900</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" t="n">
+        <v>943</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1613</v>
+      </c>
+      <c r="G9" t="n">
+        <v>980</v>
+      </c>
+      <c r="H9" t="n">
+        <v>96.22</v>
+      </c>
+      <c r="I9" t="n">
+        <v>465.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1141650.8</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/dc5_milk_run_routes.xlsx
+++ b/dc5_milk_run_routes.xlsx
@@ -493,14 +493,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DPI64758 -&gt; DPI64692 -&gt; DPI63920 -&gt; DPI70100 -&gt; DPI66659 -&gt; DPI64476 -&gt; DPI66175 -&gt; DPI66646</t>
+          <t>DPI70197 -&gt; DPI66692 -&gt; DPI64323 -&gt; DPI64746 -&gt; DPI70002 -&gt; DPI66335 -&gt; DPI66327 -&gt; DPI64484 -&gt; DPI66092 -&gt; DFT80034 -&gt; DFT80066</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="F2" t="n">
         <v>1613</v>
@@ -509,13 +509,13 @@
         <v>980</v>
       </c>
       <c r="H2" t="n">
-        <v>99.39</v>
+        <v>99.48999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>671.35</v>
+        <v>1129.75</v>
       </c>
       <c r="J2" t="n">
-        <v>1209191.12</v>
+        <v>1359589.35</v>
       </c>
     </row>
     <row r="3">
@@ -531,14 +531,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DPI64647 -&gt; DPI66421 -&gt; DPI64378 -&gt; DPI67128 -&gt; DPI64303 -&gt; DPI64255 -&gt; DPI63822</t>
+          <t>DPI63822 -&gt; DPI64378 -&gt; DPI64255 -&gt; DPI63920 -&gt; DPI66659 -&gt; DPI64476 -&gt; DPI66175 -&gt; DPI70317</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>976</v>
+        <v>980</v>
       </c>
       <c r="F3" t="n">
         <v>1613</v>
@@ -547,13 +547,13 @@
         <v>980</v>
       </c>
       <c r="H3" t="n">
-        <v>99.59</v>
+        <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>484.97</v>
+        <v>572.28</v>
       </c>
       <c r="J3" t="n">
-        <v>1148037.43</v>
+        <v>1176686.33</v>
       </c>
     </row>
     <row r="4">
@@ -569,14 +569,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DPI70179 -&gt; DPI70273 -&gt; DPI64651 -&gt; DPI66144 -&gt; DPI64746 -&gt; DPI64323 -&gt; DPI66692 -&gt; DPI64696 -&gt; DPI64104</t>
+          <t>DPI64696 -&gt; DPI64179 -&gt; DPI64651 -&gt; DPI70179 -&gt; DPI70273 -&gt; DPI66144 -&gt; DPI63847 -&gt; DPI66262 -&gt; DPI70302</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="F4" t="n">
         <v>1613</v>
@@ -585,13 +585,13 @@
         <v>980</v>
       </c>
       <c r="H4" t="n">
-        <v>98.98</v>
+        <v>98.78</v>
       </c>
       <c r="I4" t="n">
-        <v>952.55</v>
+        <v>627.15</v>
       </c>
       <c r="J4" t="n">
-        <v>1301452.02</v>
+        <v>1194686.49</v>
       </c>
     </row>
     <row r="5">
@@ -607,14 +607,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DPI64639 -&gt; DPI64044 -&gt; DPI63993 -&gt; DPI66460 -&gt; DPI64176 -&gt; DPI64234 -&gt; DPI66572 -&gt; DPI64149 -&gt; DPI70038 -&gt; DPI70073 -&gt; DPI64288 -&gt; DPI67024 -&gt; DPI70041</t>
+          <t>DPI66263 -&gt; DPI64665 -&gt; DPI64502 -&gt; DPI70120 -&gt; DPI64647 -&gt; DPI64032 -&gt; DPI66402 -&gt; DPI64409 -&gt; DPI64273</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>957</v>
+        <v>949</v>
       </c>
       <c r="F5" t="n">
         <v>1613</v>
@@ -623,13 +623,13 @@
         <v>980</v>
       </c>
       <c r="H5" t="n">
-        <v>97.65000000000001</v>
+        <v>96.84</v>
       </c>
       <c r="I5" t="n">
-        <v>1360.27</v>
+        <v>668.54</v>
       </c>
       <c r="J5" t="n">
-        <v>1435224.38</v>
+        <v>1208267.36</v>
       </c>
     </row>
     <row r="6">
@@ -645,14 +645,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DFT80081 -&gt; DFT80066 -&gt; DFT80034 -&gt; DPI66508 -&gt; DPI64511 -&gt; DPI70002 -&gt; DPI70106 -&gt; DPI64236 -&gt; DPI66734 -&gt; DPI64352 -&gt; DPI67031 -&gt; DPI66684</t>
+          <t>DPI66900 -&gt; DFT80087 -&gt; DPI64559 -&gt; DPI66229 -&gt; DPI63817 -&gt; DPI63895 -&gt; DPI64511 -&gt; DPI66508 -&gt; DPI70106 -&gt; DFT80081</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>936</v>
+        <v>973</v>
       </c>
       <c r="F6" t="n">
         <v>1613</v>
@@ -661,13 +661,13 @@
         <v>980</v>
       </c>
       <c r="H6" t="n">
-        <v>95.51000000000001</v>
+        <v>99.29000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>1133.02</v>
+        <v>609.6799999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>1360662.66</v>
+        <v>1188957.26</v>
       </c>
     </row>
     <row r="7">
@@ -683,14 +683,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DPI66092 -&gt; DPI64484 -&gt; DPI66327 -&gt; DPI63895 -&gt; DPI66335 -&gt; DPI63817 -&gt; DPI66229 -&gt; DPI64559 -&gt; DFT80087 -&gt; DPI70302</t>
+          <t>DPI66684 -&gt; DPI64236 -&gt; DPI66734 -&gt; DPI70073 -&gt; DPI70038 -&gt; DPI64149 -&gt; DPI66572 -&gt; DPI64234 -&gt; DPI64176 -&gt; DPI66460 -&gt; DPI63993 -&gt; DPI64044 -&gt; DPI64639</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E7" t="n">
-        <v>966</v>
+        <v>945</v>
       </c>
       <c r="F7" t="n">
         <v>1613</v>
@@ -699,13 +699,13 @@
         <v>980</v>
       </c>
       <c r="H7" t="n">
-        <v>98.56999999999999</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>530.62</v>
+        <v>1342.06</v>
       </c>
       <c r="J7" t="n">
-        <v>1163017.46</v>
+        <v>1429248.42</v>
       </c>
     </row>
     <row r="8">
@@ -721,14 +721,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DPI66263 -&gt; DPI64665 -&gt; DPI64502 -&gt; DPI70120 -&gt; DPI66402 -&gt; DPI64032 -&gt; DPI64409 -&gt; DPI66528 -&gt; DPI67198 -&gt; DPI70317</t>
+          <t>DPI64758 -&gt; DPI66421 -&gt; DPI67128 -&gt; DPI70100 -&gt; DPI64303 -&gt; DPI66528 -&gt; DPI64692 -&gt; DPI67198</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="F8" t="n">
         <v>1613</v>
@@ -737,13 +737,13 @@
         <v>980</v>
       </c>
       <c r="H8" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I8" t="n">
-        <v>632.4400000000001</v>
+        <v>482.28</v>
       </c>
       <c r="J8" t="n">
-        <v>1196423.54</v>
+        <v>1147155.19</v>
       </c>
     </row>
     <row r="9">
@@ -759,14 +759,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DPI66264 -&gt; DPI64273 -&gt; DPI64179 -&gt; DPI63847 -&gt; DPI66262 -&gt; DPI70197 -&gt; DPI66900</t>
+          <t>DPI64104 -&gt; DPI66646 -&gt; DPI70041 -&gt; DPI67024 -&gt; DPI64288 -&gt; DPI64352 -&gt; DPI67031 -&gt; DPI66264</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>943</v>
+        <v>931</v>
       </c>
       <c r="F9" t="n">
         <v>1613</v>
@@ -775,13 +775,13 @@
         <v>980</v>
       </c>
       <c r="H9" t="n">
-        <v>96.22</v>
+        <v>95</v>
       </c>
       <c r="I9" t="n">
-        <v>465.5</v>
+        <v>920.58</v>
       </c>
       <c r="J9" t="n">
-        <v>1141650.8</v>
+        <v>1290962.38</v>
       </c>
     </row>
   </sheetData>

--- a/dc5_milk_run_routes.xlsx
+++ b/dc5_milk_run_routes.xlsx
@@ -531,14 +531,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DPI63822 -&gt; DPI64378 -&gt; DPI64255 -&gt; DPI63920 -&gt; DPI66659 -&gt; DPI64476 -&gt; DPI66175 -&gt; DPI70317</t>
+          <t>DPI64273 -&gt; DPI64665 -&gt; DPI66263 -&gt; DPI64502 -&gt; DPI70120 -&gt; DPI64647 -&gt; DPI64032 -&gt; DPI66402 -&gt; DPI64758</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>980</v>
+        <v>956</v>
       </c>
       <c r="F3" t="n">
         <v>1613</v>
@@ -547,13 +547,13 @@
         <v>980</v>
       </c>
       <c r="H3" t="n">
-        <v>100</v>
+        <v>97.55</v>
       </c>
       <c r="I3" t="n">
-        <v>572.28</v>
+        <v>603.8200000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>1176686.33</v>
+        <v>1187034.55</v>
       </c>
     </row>
     <row r="4">
@@ -569,7 +569,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DPI64696 -&gt; DPI64179 -&gt; DPI64651 -&gt; DPI70179 -&gt; DPI70273 -&gt; DPI66144 -&gt; DPI63847 -&gt; DPI66262 -&gt; DPI70302</t>
+          <t>DPI70302 -&gt; DPI66262 -&gt; DPI70273 -&gt; DPI70179 -&gt; DPI64651 -&gt; DPI66144 -&gt; DPI63847 -&gt; DPI64179 -&gt; DPI64696</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -588,10 +588,10 @@
         <v>98.78</v>
       </c>
       <c r="I4" t="n">
-        <v>627.15</v>
+        <v>627.39</v>
       </c>
       <c r="J4" t="n">
-        <v>1194686.49</v>
+        <v>1194766.18</v>
       </c>
     </row>
     <row r="5">
@@ -607,14 +607,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DPI66263 -&gt; DPI64665 -&gt; DPI64502 -&gt; DPI70120 -&gt; DPI64647 -&gt; DPI64032 -&gt; DPI66402 -&gt; DPI64409 -&gt; DPI64273</t>
+          <t>DPI63822 -&gt; DPI64378 -&gt; DPI64255 -&gt; DPI63920 -&gt; DPI66659 -&gt; DPI64476 -&gt; DPI66175 -&gt; DPI70317</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>949</v>
+        <v>980</v>
       </c>
       <c r="F5" t="n">
         <v>1613</v>
@@ -623,13 +623,13 @@
         <v>980</v>
       </c>
       <c r="H5" t="n">
-        <v>96.84</v>
+        <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>668.54</v>
+        <v>572.28</v>
       </c>
       <c r="J5" t="n">
-        <v>1208267.36</v>
+        <v>1176686.33</v>
       </c>
     </row>
     <row r="6">
@@ -683,14 +683,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DPI66684 -&gt; DPI64236 -&gt; DPI66734 -&gt; DPI70073 -&gt; DPI70038 -&gt; DPI64149 -&gt; DPI66572 -&gt; DPI64234 -&gt; DPI64176 -&gt; DPI66460 -&gt; DPI63993 -&gt; DPI64044 -&gt; DPI64639</t>
+          <t>DPI66264 -&gt; DPI66684 -&gt; DPI67031 -&gt; DPI64352 -&gt; DPI64288 -&gt; DPI67024 -&gt; DPI70041 -&gt; DPI66646</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>945</v>
+        <v>918</v>
       </c>
       <c r="F7" t="n">
         <v>1613</v>
@@ -699,13 +699,13 @@
         <v>980</v>
       </c>
       <c r="H7" t="n">
-        <v>96.43000000000001</v>
+        <v>93.67</v>
       </c>
       <c r="I7" t="n">
-        <v>1342.06</v>
+        <v>915.98</v>
       </c>
       <c r="J7" t="n">
-        <v>1429248.42</v>
+        <v>1289452.67</v>
       </c>
     </row>
     <row r="8">
@@ -721,14 +721,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DPI64758 -&gt; DPI66421 -&gt; DPI67128 -&gt; DPI70100 -&gt; DPI64303 -&gt; DPI66528 -&gt; DPI64692 -&gt; DPI67198</t>
+          <t>DPI64104 -&gt; DPI64236 -&gt; DPI66734 -&gt; DPI70073 -&gt; DPI70038 -&gt; DPI64149 -&gt; DPI66572 -&gt; DPI64234 -&gt; DPI64176 -&gt; DPI66460 -&gt; DPI63993 -&gt; DPI64044 -&gt; DPI64639</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E8" t="n">
-        <v>980</v>
+        <v>958</v>
       </c>
       <c r="F8" t="n">
         <v>1613</v>
@@ -737,13 +737,13 @@
         <v>980</v>
       </c>
       <c r="H8" t="n">
-        <v>100</v>
+        <v>97.76000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>482.28</v>
+        <v>1345.7</v>
       </c>
       <c r="J8" t="n">
-        <v>1147155.19</v>
+        <v>1430444.75</v>
       </c>
     </row>
     <row r="9">
@@ -759,14 +759,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DPI64104 -&gt; DPI66646 -&gt; DPI70041 -&gt; DPI67024 -&gt; DPI64288 -&gt; DPI64352 -&gt; DPI67031 -&gt; DPI66264</t>
+          <t>DPI64409 -&gt; DPI66421 -&gt; DPI67128 -&gt; DPI70100 -&gt; DPI64303 -&gt; DPI66528 -&gt; DPI64692 -&gt; DPI67198</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>931</v>
+        <v>973</v>
       </c>
       <c r="F9" t="n">
         <v>1613</v>
@@ -775,13 +775,13 @@
         <v>980</v>
       </c>
       <c r="H9" t="n">
-        <v>95</v>
+        <v>99.29000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>920.58</v>
+        <v>483.9</v>
       </c>
       <c r="J9" t="n">
-        <v>1290962.38</v>
+        <v>1147686.69</v>
       </c>
     </row>
   </sheetData>

--- a/dc5_milk_run_routes.xlsx
+++ b/dc5_milk_run_routes.xlsx
@@ -531,14 +531,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DPI64273 -&gt; DPI64665 -&gt; DPI66263 -&gt; DPI64502 -&gt; DPI70120 -&gt; DPI64647 -&gt; DPI64032 -&gt; DPI66402 -&gt; DPI64758</t>
+          <t>DPI63822 -&gt; DPI64378 -&gt; DPI64255 -&gt; DPI63920 -&gt; DPI66659 -&gt; DPI64476 -&gt; DPI66175 -&gt; DPI70317</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>956</v>
+        <v>980</v>
       </c>
       <c r="F3" t="n">
         <v>1613</v>
@@ -547,13 +547,13 @@
         <v>980</v>
       </c>
       <c r="H3" t="n">
-        <v>97.55</v>
+        <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>603.8200000000001</v>
+        <v>572.28</v>
       </c>
       <c r="J3" t="n">
-        <v>1187034.55</v>
+        <v>1176686.33</v>
       </c>
     </row>
     <row r="4">
@@ -569,7 +569,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DPI70302 -&gt; DPI66262 -&gt; DPI70273 -&gt; DPI70179 -&gt; DPI64651 -&gt; DPI66144 -&gt; DPI63847 -&gt; DPI64179 -&gt; DPI64696</t>
+          <t>DPI64696 -&gt; DPI64179 -&gt; DPI64651 -&gt; DPI70179 -&gt; DPI70273 -&gt; DPI66144 -&gt; DPI63847 -&gt; DPI66262 -&gt; DPI70302</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -588,10 +588,10 @@
         <v>98.78</v>
       </c>
       <c r="I4" t="n">
-        <v>627.39</v>
+        <v>627.15</v>
       </c>
       <c r="J4" t="n">
-        <v>1194766.18</v>
+        <v>1194686.49</v>
       </c>
     </row>
     <row r="5">
@@ -607,14 +607,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DPI63822 -&gt; DPI64378 -&gt; DPI64255 -&gt; DPI63920 -&gt; DPI66659 -&gt; DPI64476 -&gt; DPI66175 -&gt; DPI70317</t>
+          <t>DPI66263 -&gt; DPI64665 -&gt; DPI64502 -&gt; DPI70120 -&gt; DPI64647 -&gt; DPI64032 -&gt; DPI66402 -&gt; DPI64409 -&gt; DPI64273</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>980</v>
+        <v>949</v>
       </c>
       <c r="F5" t="n">
         <v>1613</v>
@@ -623,13 +623,13 @@
         <v>980</v>
       </c>
       <c r="H5" t="n">
-        <v>100</v>
+        <v>96.84</v>
       </c>
       <c r="I5" t="n">
-        <v>572.28</v>
+        <v>668.54</v>
       </c>
       <c r="J5" t="n">
-        <v>1176686.33</v>
+        <v>1208267.36</v>
       </c>
     </row>
     <row r="6">
@@ -683,14 +683,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DPI66264 -&gt; DPI66684 -&gt; DPI67031 -&gt; DPI64352 -&gt; DPI64288 -&gt; DPI67024 -&gt; DPI70041 -&gt; DPI66646</t>
+          <t>DPI66684 -&gt; DPI64236 -&gt; DPI66734 -&gt; DPI70073 -&gt; DPI70038 -&gt; DPI64149 -&gt; DPI66572 -&gt; DPI64234 -&gt; DPI64176 -&gt; DPI66460 -&gt; DPI63993 -&gt; DPI64044 -&gt; DPI64639</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E7" t="n">
-        <v>918</v>
+        <v>945</v>
       </c>
       <c r="F7" t="n">
         <v>1613</v>
@@ -699,13 +699,13 @@
         <v>980</v>
       </c>
       <c r="H7" t="n">
-        <v>93.67</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>915.98</v>
+        <v>1342.06</v>
       </c>
       <c r="J7" t="n">
-        <v>1289452.67</v>
+        <v>1429248.42</v>
       </c>
     </row>
     <row r="8">
@@ -721,14 +721,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DPI64104 -&gt; DPI64236 -&gt; DPI66734 -&gt; DPI70073 -&gt; DPI70038 -&gt; DPI64149 -&gt; DPI66572 -&gt; DPI64234 -&gt; DPI64176 -&gt; DPI66460 -&gt; DPI63993 -&gt; DPI64044 -&gt; DPI64639</t>
+          <t>DPI64758 -&gt; DPI66421 -&gt; DPI67128 -&gt; DPI70100 -&gt; DPI64303 -&gt; DPI66528 -&gt; DPI64692 -&gt; DPI67198</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>958</v>
+        <v>980</v>
       </c>
       <c r="F8" t="n">
         <v>1613</v>
@@ -737,13 +737,13 @@
         <v>980</v>
       </c>
       <c r="H8" t="n">
-        <v>97.76000000000001</v>
+        <v>100</v>
       </c>
       <c r="I8" t="n">
-        <v>1345.7</v>
+        <v>482.28</v>
       </c>
       <c r="J8" t="n">
-        <v>1430444.75</v>
+        <v>1147155.19</v>
       </c>
     </row>
     <row r="9">
@@ -759,14 +759,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DPI64409 -&gt; DPI66421 -&gt; DPI67128 -&gt; DPI70100 -&gt; DPI64303 -&gt; DPI66528 -&gt; DPI64692 -&gt; DPI67198</t>
+          <t>DPI64104 -&gt; DPI66646 -&gt; DPI70041 -&gt; DPI67024 -&gt; DPI64288 -&gt; DPI64352 -&gt; DPI67031 -&gt; DPI66264</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>973</v>
+        <v>931</v>
       </c>
       <c r="F9" t="n">
         <v>1613</v>
@@ -775,13 +775,13 @@
         <v>980</v>
       </c>
       <c r="H9" t="n">
-        <v>99.29000000000001</v>
+        <v>95</v>
       </c>
       <c r="I9" t="n">
-        <v>483.9</v>
+        <v>920.58</v>
       </c>
       <c r="J9" t="n">
-        <v>1147686.69</v>
+        <v>1290962.38</v>
       </c>
     </row>
   </sheetData>

--- a/dc5_milk_run_routes.xlsx
+++ b/dc5_milk_run_routes.xlsx
@@ -493,14 +493,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DPI70197 -&gt; DPI66692 -&gt; DPI64323 -&gt; DPI64746 -&gt; DPI70002 -&gt; DPI66335 -&gt; DPI66327 -&gt; DPI64484 -&gt; DPI66092 -&gt; DFT80034 -&gt; DFT80066</t>
+          <t>DPI66264 -&gt; DPI66684 -&gt; DPI67031 -&gt; DPI70073 -&gt; DPI70038 -&gt; DPI64149 -&gt; DPI66572 -&gt; DPI64234 -&gt; DPI64176 -&gt; DPI66460 -&gt; DPI63993 -&gt; DPI64044</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="F2" t="n">
         <v>1613</v>
@@ -509,13 +509,13 @@
         <v>980</v>
       </c>
       <c r="H2" t="n">
-        <v>99.48999999999999</v>
+        <v>99.08</v>
       </c>
       <c r="I2" t="n">
-        <v>1129.75</v>
+        <v>1333.75</v>
       </c>
       <c r="J2" t="n">
-        <v>1359589.35</v>
+        <v>1426521.87</v>
       </c>
     </row>
     <row r="3">
@@ -531,14 +531,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DPI63822 -&gt; DPI64378 -&gt; DPI64255 -&gt; DPI63920 -&gt; DPI66659 -&gt; DPI64476 -&gt; DPI66175 -&gt; DPI70317</t>
+          <t>DPI64665 -&gt; DPI66263 -&gt; DPI64502 -&gt; DPI70120 -&gt; DPI64409 -&gt; DPI70100 -&gt; DPI64476 -&gt; DPI66175 -&gt; DPI66646</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="F3" t="n">
         <v>1613</v>
@@ -547,13 +547,13 @@
         <v>980</v>
       </c>
       <c r="H3" t="n">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="I3" t="n">
-        <v>572.28</v>
+        <v>804.84</v>
       </c>
       <c r="J3" t="n">
-        <v>1176686.33</v>
+        <v>1252986.89</v>
       </c>
     </row>
     <row r="4">
@@ -569,14 +569,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DPI64696 -&gt; DPI64179 -&gt; DPI64651 -&gt; DPI70179 -&gt; DPI70273 -&gt; DPI66144 -&gt; DPI63847 -&gt; DPI66262 -&gt; DPI70302</t>
+          <t>DPI63822 -&gt; DPI66421 -&gt; DPI64303 -&gt; DPI63920 -&gt; DPI66528 -&gt; DPI64692 -&gt; DPI67198</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>968</v>
+        <v>979</v>
       </c>
       <c r="F4" t="n">
         <v>1613</v>
@@ -585,13 +585,13 @@
         <v>980</v>
       </c>
       <c r="H4" t="n">
-        <v>98.78</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>627.15</v>
+        <v>481.84</v>
       </c>
       <c r="J4" t="n">
-        <v>1194686.49</v>
+        <v>1147013.06</v>
       </c>
     </row>
     <row r="5">
@@ -607,14 +607,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DPI66263 -&gt; DPI64665 -&gt; DPI64502 -&gt; DPI70120 -&gt; DPI64647 -&gt; DPI64032 -&gt; DPI66402 -&gt; DPI64409 -&gt; DPI64273</t>
+          <t>DFT80066 -&gt; DPI66092 -&gt; DPI66327 -&gt; DPI64559 -&gt; DFT80087 -&gt; DPI64651 -&gt; DPI66144 -&gt; DPI63847 -&gt; DPI70197 -&gt; DPI66900</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>949</v>
+        <v>972</v>
       </c>
       <c r="F5" t="n">
         <v>1613</v>
@@ -623,13 +623,13 @@
         <v>980</v>
       </c>
       <c r="H5" t="n">
-        <v>96.84</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>668.54</v>
+        <v>555.5700000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>1208267.36</v>
+        <v>1171201.09</v>
       </c>
     </row>
     <row r="6">
@@ -645,14 +645,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DPI66900 -&gt; DFT80087 -&gt; DPI64559 -&gt; DPI66229 -&gt; DPI63817 -&gt; DPI63895 -&gt; DPI64511 -&gt; DPI66508 -&gt; DPI70106 -&gt; DFT80081</t>
+          <t>DPI64104 -&gt; DPI64273 -&gt; DPI64696 -&gt; DPI66692 -&gt; DPI64323 -&gt; DPI64746 -&gt; DPI64179</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>973</v>
+        <v>879</v>
       </c>
       <c r="F6" t="n">
         <v>1613</v>
@@ -661,13 +661,13 @@
         <v>980</v>
       </c>
       <c r="H6" t="n">
-        <v>99.29000000000001</v>
+        <v>89.69</v>
       </c>
       <c r="I6" t="n">
-        <v>609.6799999999999</v>
+        <v>935.14</v>
       </c>
       <c r="J6" t="n">
-        <v>1188957.26</v>
+        <v>1295738.47</v>
       </c>
     </row>
     <row r="7">
@@ -683,14 +683,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DPI66684 -&gt; DPI64236 -&gt; DPI66734 -&gt; DPI70073 -&gt; DPI70038 -&gt; DPI64149 -&gt; DPI66572 -&gt; DPI64234 -&gt; DPI64176 -&gt; DPI66460 -&gt; DPI63993 -&gt; DPI64044 -&gt; DPI64639</t>
+          <t>DPI70317 -&gt; DPI66659 -&gt; DPI64255 -&gt; DPI67128 -&gt; DPI64378 -&gt; DPI66402 -&gt; DPI64032 -&gt; DPI64647 -&gt; DPI64758</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>945</v>
+        <v>972</v>
       </c>
       <c r="F7" t="n">
         <v>1613</v>
@@ -699,13 +699,13 @@
         <v>980</v>
       </c>
       <c r="H7" t="n">
-        <v>96.43000000000001</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>1342.06</v>
+        <v>511.23</v>
       </c>
       <c r="J7" t="n">
-        <v>1429248.42</v>
+        <v>1156655.59</v>
       </c>
     </row>
     <row r="8">
@@ -721,14 +721,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DPI64758 -&gt; DPI66421 -&gt; DPI67128 -&gt; DPI70100 -&gt; DPI64303 -&gt; DPI66528 -&gt; DPI64692 -&gt; DPI67198</t>
+          <t>DPI66229 -&gt; DPI66335 -&gt; DPI70106 -&gt; DPI64639 -&gt; DPI64236 -&gt; DPI66734 -&gt; DPI64352 -&gt; DPI64288 -&gt; DPI67024 -&gt; DPI70041</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="F8" t="n">
         <v>1613</v>
@@ -737,13 +737,13 @@
         <v>980</v>
       </c>
       <c r="H8" t="n">
-        <v>100</v>
+        <v>99.69</v>
       </c>
       <c r="I8" t="n">
-        <v>482.28</v>
+        <v>1147.85</v>
       </c>
       <c r="J8" t="n">
-        <v>1147155.19</v>
+        <v>1365529.24</v>
       </c>
     </row>
     <row r="9">
@@ -759,14 +759,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DPI64104 -&gt; DPI66646 -&gt; DPI70041 -&gt; DPI67024 -&gt; DPI64288 -&gt; DPI64352 -&gt; DPI67031 -&gt; DPI66264</t>
+          <t>DPI70179 -&gt; DPI70273 -&gt; DPI66262 -&gt; DPI70302 -&gt; DPI70002 -&gt; DPI64511 -&gt; DPI63895 -&gt; DPI63817 -&gt; DPI64484 -&gt; DPI66508 -&gt; DFT80034 -&gt; DFT80081</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>931</v>
+        <v>973</v>
       </c>
       <c r="F9" t="n">
         <v>1613</v>
@@ -775,13 +775,13 @@
         <v>980</v>
       </c>
       <c r="H9" t="n">
-        <v>95</v>
+        <v>99.29000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>920.58</v>
+        <v>599.77</v>
       </c>
       <c r="J9" t="n">
-        <v>1290962.38</v>
+        <v>1185705.73</v>
       </c>
     </row>
   </sheetData>

--- a/dc5_milk_run_routes.xlsx
+++ b/dc5_milk_run_routes.xlsx
@@ -493,14 +493,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DPI66264 -&gt; DPI66684 -&gt; DPI67031 -&gt; DPI70073 -&gt; DPI70038 -&gt; DPI64149 -&gt; DPI66572 -&gt; DPI64234 -&gt; DPI64176 -&gt; DPI66460 -&gt; DPI63993 -&gt; DPI64044</t>
+          <t>DPI70197 -&gt; DPI66692 -&gt; DPI64323 -&gt; DPI64746 -&gt; DPI70002 -&gt; DPI66335 -&gt; DPI66327 -&gt; DPI64484 -&gt; DPI66092 -&gt; DFT80034 -&gt; DFT80066</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>971</v>
+        <v>975</v>
       </c>
       <c r="F2" t="n">
         <v>1613</v>
@@ -509,13 +509,13 @@
         <v>980</v>
       </c>
       <c r="H2" t="n">
-        <v>99.08</v>
+        <v>99.48999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>1333.75</v>
+        <v>1129.75</v>
       </c>
       <c r="J2" t="n">
-        <v>1426521.87</v>
+        <v>1359589.35</v>
       </c>
     </row>
     <row r="3">
@@ -531,14 +531,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DPI64665 -&gt; DPI66263 -&gt; DPI64502 -&gt; DPI70120 -&gt; DPI64409 -&gt; DPI70100 -&gt; DPI64476 -&gt; DPI66175 -&gt; DPI66646</t>
+          <t>DPI63822 -&gt; DPI64378 -&gt; DPI64255 -&gt; DPI63920 -&gt; DPI66659 -&gt; DPI64476 -&gt; DPI66175 -&gt; DPI70317</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="F3" t="n">
         <v>1613</v>
@@ -547,13 +547,13 @@
         <v>980</v>
       </c>
       <c r="H3" t="n">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>804.84</v>
+        <v>572.28</v>
       </c>
       <c r="J3" t="n">
-        <v>1252986.89</v>
+        <v>1176686.33</v>
       </c>
     </row>
     <row r="4">
@@ -569,14 +569,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DPI63822 -&gt; DPI66421 -&gt; DPI64303 -&gt; DPI63920 -&gt; DPI66528 -&gt; DPI64692 -&gt; DPI67198</t>
+          <t>DPI64696 -&gt; DPI64179 -&gt; DPI64651 -&gt; DPI70179 -&gt; DPI70273 -&gt; DPI66144 -&gt; DPI63847 -&gt; DPI66262 -&gt; DPI70302</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>979</v>
+        <v>968</v>
       </c>
       <c r="F4" t="n">
         <v>1613</v>
@@ -585,13 +585,13 @@
         <v>980</v>
       </c>
       <c r="H4" t="n">
-        <v>99.90000000000001</v>
+        <v>98.78</v>
       </c>
       <c r="I4" t="n">
-        <v>481.84</v>
+        <v>627.15</v>
       </c>
       <c r="J4" t="n">
-        <v>1147013.06</v>
+        <v>1194686.49</v>
       </c>
     </row>
     <row r="5">
@@ -607,14 +607,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DFT80066 -&gt; DPI66092 -&gt; DPI66327 -&gt; DPI64559 -&gt; DFT80087 -&gt; DPI64651 -&gt; DPI66144 -&gt; DPI63847 -&gt; DPI70197 -&gt; DPI66900</t>
+          <t>DPI66263 -&gt; DPI64665 -&gt; DPI64502 -&gt; DPI70120 -&gt; DPI64647 -&gt; DPI64032 -&gt; DPI66402 -&gt; DPI64409 -&gt; DPI64273</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>972</v>
+        <v>949</v>
       </c>
       <c r="F5" t="n">
         <v>1613</v>
@@ -623,13 +623,13 @@
         <v>980</v>
       </c>
       <c r="H5" t="n">
-        <v>99.18000000000001</v>
+        <v>96.84</v>
       </c>
       <c r="I5" t="n">
-        <v>555.5700000000001</v>
+        <v>668.54</v>
       </c>
       <c r="J5" t="n">
-        <v>1171201.09</v>
+        <v>1208267.36</v>
       </c>
     </row>
     <row r="6">
@@ -645,14 +645,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DPI64104 -&gt; DPI64273 -&gt; DPI64696 -&gt; DPI66692 -&gt; DPI64323 -&gt; DPI64746 -&gt; DPI64179</t>
+          <t>DPI66900 -&gt; DFT80087 -&gt; DPI64559 -&gt; DPI66229 -&gt; DPI63817 -&gt; DPI63895 -&gt; DPI64511 -&gt; DPI66508 -&gt; DPI70106 -&gt; DFT80081</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>879</v>
+        <v>973</v>
       </c>
       <c r="F6" t="n">
         <v>1613</v>
@@ -661,13 +661,13 @@
         <v>980</v>
       </c>
       <c r="H6" t="n">
-        <v>89.69</v>
+        <v>99.29000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>935.14</v>
+        <v>609.6799999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>1295738.47</v>
+        <v>1188957.26</v>
       </c>
     </row>
     <row r="7">
@@ -683,14 +683,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DPI70317 -&gt; DPI66659 -&gt; DPI64255 -&gt; DPI67128 -&gt; DPI64378 -&gt; DPI66402 -&gt; DPI64032 -&gt; DPI64647 -&gt; DPI64758</t>
+          <t>DPI66684 -&gt; DPI64236 -&gt; DPI66734 -&gt; DPI70073 -&gt; DPI70038 -&gt; DPI64149 -&gt; DPI66572 -&gt; DPI64234 -&gt; DPI64176 -&gt; DPI66460 -&gt; DPI63993 -&gt; DPI64044 -&gt; DPI64639</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E7" t="n">
-        <v>972</v>
+        <v>945</v>
       </c>
       <c r="F7" t="n">
         <v>1613</v>
@@ -699,13 +699,13 @@
         <v>980</v>
       </c>
       <c r="H7" t="n">
-        <v>99.18000000000001</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>511.23</v>
+        <v>1342.06</v>
       </c>
       <c r="J7" t="n">
-        <v>1156655.59</v>
+        <v>1429248.42</v>
       </c>
     </row>
     <row r="8">
@@ -721,14 +721,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DPI66229 -&gt; DPI66335 -&gt; DPI70106 -&gt; DPI64639 -&gt; DPI64236 -&gt; DPI66734 -&gt; DPI64352 -&gt; DPI64288 -&gt; DPI67024 -&gt; DPI70041</t>
+          <t>DPI64758 -&gt; DPI66421 -&gt; DPI67128 -&gt; DPI70100 -&gt; DPI64303 -&gt; DPI66528 -&gt; DPI64692 -&gt; DPI67198</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="F8" t="n">
         <v>1613</v>
@@ -737,13 +737,13 @@
         <v>980</v>
       </c>
       <c r="H8" t="n">
-        <v>99.69</v>
+        <v>100</v>
       </c>
       <c r="I8" t="n">
-        <v>1147.85</v>
+        <v>482.28</v>
       </c>
       <c r="J8" t="n">
-        <v>1365529.24</v>
+        <v>1147155.19</v>
       </c>
     </row>
     <row r="9">
@@ -759,14 +759,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DPI70179 -&gt; DPI70273 -&gt; DPI66262 -&gt; DPI70302 -&gt; DPI70002 -&gt; DPI64511 -&gt; DPI63895 -&gt; DPI63817 -&gt; DPI64484 -&gt; DPI66508 -&gt; DFT80034 -&gt; DFT80081</t>
+          <t>DPI64104 -&gt; DPI66646 -&gt; DPI70041 -&gt; DPI67024 -&gt; DPI64288 -&gt; DPI64352 -&gt; DPI67031 -&gt; DPI66264</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>973</v>
+        <v>931</v>
       </c>
       <c r="F9" t="n">
         <v>1613</v>
@@ -775,13 +775,13 @@
         <v>980</v>
       </c>
       <c r="H9" t="n">
-        <v>99.29000000000001</v>
+        <v>95</v>
       </c>
       <c r="I9" t="n">
-        <v>599.77</v>
+        <v>920.58</v>
       </c>
       <c r="J9" t="n">
-        <v>1185705.73</v>
+        <v>1290962.38</v>
       </c>
     </row>
   </sheetData>

--- a/dc5_milk_run_routes.xlsx
+++ b/dc5_milk_run_routes.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DPI63822 -&gt; DPI64378 -&gt; DPI64255 -&gt; DPI63920 -&gt; DPI66659 -&gt; DPI64476 -&gt; DPI66175 -&gt; DPI70317</t>
+          <t>DPI64255 -&gt; DPI63822 -&gt; DPI64378 -&gt; DPI63920 -&gt; DPI66659 -&gt; DPI64476 -&gt; DPI66175 -&gt; DPI70317</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -626,10 +626,10 @@
         <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>572.28</v>
+        <v>580.47</v>
       </c>
       <c r="J5" t="n">
-        <v>1176686.33</v>
+        <v>1179372.29</v>
       </c>
     </row>
     <row r="6">

--- a/dc5_milk_run_routes.xlsx
+++ b/dc5_milk_run_routes.xlsx
@@ -531,14 +531,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DPI64273 -&gt; DPI64665 -&gt; DPI66263 -&gt; DPI64502 -&gt; DPI70120 -&gt; DPI64647 -&gt; DPI64032 -&gt; DPI66402 -&gt; DPI64758</t>
+          <t>DPI63822 -&gt; DPI64378 -&gt; DPI64255 -&gt; DPI63920 -&gt; DPI66659 -&gt; DPI64476 -&gt; DPI66175 -&gt; DPI70317</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>956</v>
+        <v>980</v>
       </c>
       <c r="F3" t="n">
         <v>1613</v>
@@ -547,13 +547,13 @@
         <v>980</v>
       </c>
       <c r="H3" t="n">
-        <v>97.55</v>
+        <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>603.8200000000001</v>
+        <v>572.28</v>
       </c>
       <c r="J3" t="n">
-        <v>1187034.55</v>
+        <v>1176686.33</v>
       </c>
     </row>
     <row r="4">
@@ -569,7 +569,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DPI70302 -&gt; DPI66262 -&gt; DPI70273 -&gt; DPI70179 -&gt; DPI64651 -&gt; DPI66144 -&gt; DPI63847 -&gt; DPI64179 -&gt; DPI64696</t>
+          <t>DPI64696 -&gt; DPI64179 -&gt; DPI64651 -&gt; DPI70179 -&gt; DPI70273 -&gt; DPI66144 -&gt; DPI63847 -&gt; DPI66262 -&gt; DPI70302</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -588,10 +588,10 @@
         <v>98.78</v>
       </c>
       <c r="I4" t="n">
-        <v>627.39</v>
+        <v>627.15</v>
       </c>
       <c r="J4" t="n">
-        <v>1194766.18</v>
+        <v>1194686.49</v>
       </c>
     </row>
     <row r="5">
@@ -607,14 +607,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DPI64255 -&gt; DPI63822 -&gt; DPI64378 -&gt; DPI63920 -&gt; DPI66659 -&gt; DPI64476 -&gt; DPI66175 -&gt; DPI70317</t>
+          <t>DPI66263 -&gt; DPI64665 -&gt; DPI64502 -&gt; DPI70120 -&gt; DPI64647 -&gt; DPI64032 -&gt; DPI66402 -&gt; DPI64409 -&gt; DPI64273</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>980</v>
+        <v>949</v>
       </c>
       <c r="F5" t="n">
         <v>1613</v>
@@ -623,13 +623,13 @@
         <v>980</v>
       </c>
       <c r="H5" t="n">
-        <v>100</v>
+        <v>96.84</v>
       </c>
       <c r="I5" t="n">
-        <v>580.47</v>
+        <v>668.54</v>
       </c>
       <c r="J5" t="n">
-        <v>1179372.29</v>
+        <v>1208267.36</v>
       </c>
     </row>
     <row r="6">
@@ -683,14 +683,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DPI66264 -&gt; DPI66684 -&gt; DPI67031 -&gt; DPI64352 -&gt; DPI64288 -&gt; DPI67024 -&gt; DPI70041 -&gt; DPI66646</t>
+          <t>DPI66684 -&gt; DPI64236 -&gt; DPI66734 -&gt; DPI70073 -&gt; DPI70038 -&gt; DPI64149 -&gt; DPI66572 -&gt; DPI64234 -&gt; DPI64176 -&gt; DPI66460 -&gt; DPI63993 -&gt; DPI64044 -&gt; DPI64639</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E7" t="n">
-        <v>918</v>
+        <v>945</v>
       </c>
       <c r="F7" t="n">
         <v>1613</v>
@@ -699,13 +699,13 @@
         <v>980</v>
       </c>
       <c r="H7" t="n">
-        <v>93.67</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>915.98</v>
+        <v>1342.06</v>
       </c>
       <c r="J7" t="n">
-        <v>1289452.67</v>
+        <v>1429248.42</v>
       </c>
     </row>
     <row r="8">
@@ -721,14 +721,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DPI64104 -&gt; DPI64236 -&gt; DPI66734 -&gt; DPI70073 -&gt; DPI70038 -&gt; DPI64149 -&gt; DPI66572 -&gt; DPI64234 -&gt; DPI64176 -&gt; DPI66460 -&gt; DPI63993 -&gt; DPI64044 -&gt; DPI64639</t>
+          <t>DPI64758 -&gt; DPI66421 -&gt; DPI67128 -&gt; DPI70100 -&gt; DPI64303 -&gt; DPI66528 -&gt; DPI64692 -&gt; DPI67198</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>958</v>
+        <v>980</v>
       </c>
       <c r="F8" t="n">
         <v>1613</v>
@@ -737,13 +737,13 @@
         <v>980</v>
       </c>
       <c r="H8" t="n">
-        <v>97.76000000000001</v>
+        <v>100</v>
       </c>
       <c r="I8" t="n">
-        <v>1345.7</v>
+        <v>482.28</v>
       </c>
       <c r="J8" t="n">
-        <v>1430444.75</v>
+        <v>1147155.19</v>
       </c>
     </row>
     <row r="9">
@@ -759,14 +759,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DPI64409 -&gt; DPI66421 -&gt; DPI67128 -&gt; DPI70100 -&gt; DPI64303 -&gt; DPI66528 -&gt; DPI64692 -&gt; DPI67198</t>
+          <t>DPI64104 -&gt; DPI66646 -&gt; DPI70041 -&gt; DPI67024 -&gt; DPI64288 -&gt; DPI64352 -&gt; DPI67031 -&gt; DPI66264</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>973</v>
+        <v>931</v>
       </c>
       <c r="F9" t="n">
         <v>1613</v>
@@ -775,13 +775,13 @@
         <v>980</v>
       </c>
       <c r="H9" t="n">
-        <v>99.29000000000001</v>
+        <v>95</v>
       </c>
       <c r="I9" t="n">
-        <v>483.9</v>
+        <v>920.58</v>
       </c>
       <c r="J9" t="n">
-        <v>1147686.69</v>
+        <v>1290962.38</v>
       </c>
     </row>
   </sheetData>

--- a/dc5_milk_run_routes.xlsx
+++ b/dc5_milk_run_routes.xlsx
@@ -515,7 +515,7 @@
         <v>1129.75</v>
       </c>
       <c r="J2" t="n">
-        <v>1359589.35</v>
+        <v>469561.35</v>
       </c>
     </row>
     <row r="3">
@@ -553,7 +553,7 @@
         <v>572.28</v>
       </c>
       <c r="J3" t="n">
-        <v>1176686.33</v>
+        <v>286658.33</v>
       </c>
     </row>
     <row r="4">
@@ -591,7 +591,7 @@
         <v>627.15</v>
       </c>
       <c r="J4" t="n">
-        <v>1194686.49</v>
+        <v>304658.49</v>
       </c>
     </row>
     <row r="5">
@@ -629,7 +629,7 @@
         <v>668.54</v>
       </c>
       <c r="J5" t="n">
-        <v>1208267.36</v>
+        <v>318239.36</v>
       </c>
     </row>
     <row r="6">
@@ -667,7 +667,7 @@
         <v>609.6799999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>1188957.26</v>
+        <v>298929.26</v>
       </c>
     </row>
     <row r="7">
@@ -705,7 +705,7 @@
         <v>1342.06</v>
       </c>
       <c r="J7" t="n">
-        <v>1429248.42</v>
+        <v>539220.42</v>
       </c>
     </row>
     <row r="8">
@@ -743,7 +743,7 @@
         <v>482.28</v>
       </c>
       <c r="J8" t="n">
-        <v>1147155.19</v>
+        <v>257127.19</v>
       </c>
     </row>
     <row r="9">
@@ -781,7 +781,7 @@
         <v>920.58</v>
       </c>
       <c r="J9" t="n">
-        <v>1290962.38</v>
+        <v>400934.38</v>
       </c>
     </row>
   </sheetData>
